--- a/data/3.meta_data/matrices/0034a.xlsx
+++ b/data/3.meta_data/matrices/0034a.xlsx
@@ -711,43 +711,43 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.0917872998824952</v>
+        <v>0.09178729988249522</v>
       </c>
       <c r="C2">
-        <v>0.08777777316553813</v>
+        <v>0.08777777316553811</v>
       </c>
       <c r="D2">
         <v>0.1436326379992314</v>
       </c>
       <c r="E2">
-        <v>0.0008752855493400268</v>
+        <v>0.0008752855493400349</v>
       </c>
       <c r="F2">
         <v>0.2092797640761957</v>
       </c>
       <c r="G2">
-        <v>-0.07647180455298133</v>
+        <v>-0.07647180455298136</v>
       </c>
       <c r="H2">
-        <v>0.01563934308344956</v>
+        <v>0.01563934308344957</v>
       </c>
       <c r="I2">
-        <v>-0.004203715761054981</v>
+        <v>-0.004203715761054987</v>
       </c>
       <c r="J2">
         <v>0.1662355048828534</v>
       </c>
       <c r="K2">
-        <v>0.07645635761104071</v>
+        <v>0.07645635761104069</v>
       </c>
       <c r="L2">
         <v>0.2023750242701526</v>
       </c>
       <c r="M2">
-        <v>0.1715824180361433</v>
+        <v>0.1715824180361434</v>
       </c>
       <c r="N2">
-        <v>0.08859376413208347</v>
+        <v>0.08859376413208346</v>
       </c>
       <c r="O2">
         <v>0.1563064516029841</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.0917872998824952</v>
+        <v>0.09178729988249522</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -938,13 +938,13 @@
         <v>0.4032096177431564</v>
       </c>
       <c r="G3">
-        <v>0.06697000637624108</v>
+        <v>0.06697000637624109</v>
       </c>
       <c r="H3">
         <v>0.3971324896415877</v>
       </c>
       <c r="I3">
-        <v>0.09412086861154725</v>
+        <v>0.09412086861154727</v>
       </c>
       <c r="J3">
         <v>0.3712199663767348</v>
@@ -959,7 +959,7 @@
         <v>0.3651778223942292</v>
       </c>
       <c r="N3">
-        <v>0.07840112940071385</v>
+        <v>0.07840112940071386</v>
       </c>
       <c r="O3">
         <v>0.2060543638071748</v>
@@ -983,7 +983,7 @@
         <v>0.3093857877931815</v>
       </c>
       <c r="V3">
-        <v>0.3747926604339863</v>
+        <v>0.3747926604339864</v>
       </c>
       <c r="W3">
         <v>0.148243289510646</v>
@@ -1040,13 +1040,13 @@
         <v>-0.01807728114435401</v>
       </c>
       <c r="AO3">
-        <v>0.04140704974098997</v>
+        <v>0.04140704974098999</v>
       </c>
       <c r="AP3">
-        <v>-0.2073042002127984</v>
+        <v>-0.2073042002127985</v>
       </c>
       <c r="AQ3">
-        <v>0.08300260959817199</v>
+        <v>0.083002609598172</v>
       </c>
       <c r="AR3">
         <v>0.7580741145508794</v>
@@ -1067,7 +1067,7 @@
         <v>0.3771603777923991</v>
       </c>
       <c r="AX3">
-        <v>-0.04254991443654318</v>
+        <v>-0.04254991443654316</v>
       </c>
       <c r="AY3">
         <v>0.1115269693982819</v>
@@ -1088,7 +1088,7 @@
         <v>0.2706574535603001</v>
       </c>
       <c r="BE3">
-        <v>0.1628392400525995</v>
+        <v>0.1628392400525996</v>
       </c>
       <c r="BF3">
         <v>0.3692401566692279</v>
@@ -1100,22 +1100,22 @@
         <v>0.317757538562405</v>
       </c>
       <c r="BI3">
-        <v>-0.06138882052757016</v>
+        <v>-0.06138882052757017</v>
       </c>
       <c r="BJ3">
         <v>0.3398346052965777</v>
       </c>
       <c r="BK3">
-        <v>-0.1571188328370876</v>
+        <v>-0.1571188328370877</v>
       </c>
       <c r="BL3">
-        <v>0.05000191297444864</v>
+        <v>0.05000191297444862</v>
       </c>
       <c r="BM3">
         <v>0.6624451302920801</v>
       </c>
       <c r="BN3">
-        <v>-0.08262493891472335</v>
+        <v>-0.08262493891472332</v>
       </c>
       <c r="BO3">
         <v>0.1722297273811934</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.08777777316553813</v>
+        <v>0.08777777316553811</v>
       </c>
       <c r="B4">
         <v>0.5416931627328095</v>
@@ -1171,7 +1171,7 @@
         <v>0.2971520360832904</v>
       </c>
       <c r="N4">
-        <v>0.09108327508859106</v>
+        <v>0.09108327508859104</v>
       </c>
       <c r="O4">
         <v>0.2063988744233315</v>
@@ -1192,7 +1192,7 @@
         <v>0.128767073598089</v>
       </c>
       <c r="U4">
-        <v>0.2342868726029402</v>
+        <v>0.2342868726029401</v>
       </c>
       <c r="V4">
         <v>0.4019066637526973</v>
@@ -1213,7 +1213,7 @@
         <v>0.3402145098969347</v>
       </c>
       <c r="AB4">
-        <v>0.1890404768265991</v>
+        <v>0.189040476826599</v>
       </c>
       <c r="AC4">
         <v>0.2311220657237968</v>
@@ -1222,7 +1222,7 @@
         <v>0.3124321024271509</v>
       </c>
       <c r="AE4">
-        <v>0.340779336680734</v>
+        <v>0.3407793366807339</v>
       </c>
       <c r="AF4">
         <v>0.2860621143517341</v>
@@ -1234,7 +1234,7 @@
         <v>0.7829908320766911</v>
       </c>
       <c r="AI4">
-        <v>0.5533588522479808</v>
+        <v>0.5533588522479806</v>
       </c>
       <c r="AJ4">
         <v>0.2629563875510444</v>
@@ -1246,7 +1246,7 @@
         <v>0.3316998884108447</v>
       </c>
       <c r="AM4">
-        <v>0.7425838147914058</v>
+        <v>0.7425838147914059</v>
       </c>
       <c r="AN4">
         <v>0.1916241594287605</v>
@@ -1258,10 +1258,10 @@
         <v>-0.1114386403000996</v>
       </c>
       <c r="AQ4">
-        <v>-0.001635977054502158</v>
+        <v>-0.001635977054502163</v>
       </c>
       <c r="AR4">
-        <v>0.4058312002974861</v>
+        <v>0.405831200297486</v>
       </c>
       <c r="AS4">
         <v>0.1007691536068129</v>
@@ -1282,7 +1282,7 @@
         <v>0.2080983847838686</v>
       </c>
       <c r="AY4">
-        <v>0.03447326115644708</v>
+        <v>0.03447326115644706</v>
       </c>
       <c r="AZ4">
         <v>-0.1218801066767945</v>
@@ -1300,7 +1300,7 @@
         <v>0.4057283789481878</v>
       </c>
       <c r="BE4">
-        <v>0.0386737019287409</v>
+        <v>0.03867370192874089</v>
       </c>
       <c r="BF4">
         <v>0.3367439535541316</v>
@@ -1312,7 +1312,7 @@
         <v>0.3292002001880542</v>
       </c>
       <c r="BI4">
-        <v>-0.03533065083601121</v>
+        <v>-0.0353306508360112</v>
       </c>
       <c r="BJ4">
         <v>0.1797582900543516</v>
@@ -1321,7 +1321,7 @@
         <v>-0.155519279784181</v>
       </c>
       <c r="BL4">
-        <v>0.004640505707432534</v>
+        <v>0.004640505707432542</v>
       </c>
       <c r="BM4">
         <v>0.7250714524593095</v>
@@ -1339,7 +1339,7 @@
         <v>0.1414835039872273</v>
       </c>
       <c r="BR4">
-        <v>0.007397472887378596</v>
+        <v>0.007397472887378591</v>
       </c>
     </row>
     <row r="5">
@@ -1386,10 +1386,10 @@
         <v>0.01588767646759677</v>
       </c>
       <c r="O5">
-        <v>0.1804994414204048</v>
+        <v>0.1804994414204049</v>
       </c>
       <c r="P5">
-        <v>0.2511679338560774</v>
+        <v>0.2511679338560775</v>
       </c>
       <c r="Q5">
         <v>0.2887667214370522</v>
@@ -1413,7 +1413,7 @@
         <v>0.1318978522397696</v>
       </c>
       <c r="X5">
-        <v>0.3742409163349652</v>
+        <v>0.3742409163349653</v>
       </c>
       <c r="Y5">
         <v>0.2122577325961352</v>
@@ -1458,13 +1458,13 @@
         <v>0.2962467231667319</v>
       </c>
       <c r="AM5">
-        <v>0.4319982175357553</v>
+        <v>0.4319982175357552</v>
       </c>
       <c r="AN5">
         <v>0.274936316129236</v>
       </c>
       <c r="AO5">
-        <v>-0.03700588076986108</v>
+        <v>-0.03700588076986109</v>
       </c>
       <c r="AP5">
         <v>-0.104444670628245</v>
@@ -1476,7 +1476,7 @@
         <v>0.3108419388701779</v>
       </c>
       <c r="AS5">
-        <v>0.082055304171447</v>
+        <v>0.08205530417144699</v>
       </c>
       <c r="AT5">
         <v>0.2260198766534655</v>
@@ -1497,7 +1497,7 @@
         <v>0.08929657813578637</v>
       </c>
       <c r="AZ5">
-        <v>-0.1646666226593624</v>
+        <v>-0.1646666226593623</v>
       </c>
       <c r="BA5">
         <v>0.2638856314761223</v>
@@ -1512,7 +1512,7 @@
         <v>0.2641589139127369</v>
       </c>
       <c r="BE5">
-        <v>0.07726081843365447</v>
+        <v>0.07726081843365448</v>
       </c>
       <c r="BF5">
         <v>0.2401775668345847</v>
@@ -1533,7 +1533,7 @@
         <v>-0.2203898704241405</v>
       </c>
       <c r="BL5">
-        <v>0.00975439863784475</v>
+        <v>0.009754398637844759</v>
       </c>
       <c r="BM5">
         <v>0.4577821850040105</v>
@@ -1551,12 +1551,12 @@
         <v>0.2152122242968705</v>
       </c>
       <c r="BR5">
-        <v>0.003736241288074699</v>
+        <v>0.00373624128807471</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.0008752855493400268</v>
+        <v>0.0008752855493400349</v>
       </c>
       <c r="B6">
         <v>0.7203039918602703</v>
@@ -1574,13 +1574,13 @@
         <v>0.2672242506139109</v>
       </c>
       <c r="G6">
-        <v>0.04417786151219624</v>
+        <v>0.04417786151219623</v>
       </c>
       <c r="H6">
         <v>0.3470997648761921</v>
       </c>
       <c r="I6">
-        <v>-0.02163827414123358</v>
+        <v>-0.0216382741412336</v>
       </c>
       <c r="J6">
         <v>0.2207622268517306</v>
@@ -1595,10 +1595,10 @@
         <v>0.24681863850596</v>
       </c>
       <c r="N6">
-        <v>-0.01872291362013562</v>
+        <v>-0.01872291362013559</v>
       </c>
       <c r="O6">
-        <v>0.08612642912216581</v>
+        <v>0.08612642912216582</v>
       </c>
       <c r="P6">
         <v>0.2727355779648076</v>
@@ -1622,7 +1622,7 @@
         <v>0.2409969723637757</v>
       </c>
       <c r="W6">
-        <v>0.0001185471298084199</v>
+        <v>0.0001185471298084107</v>
       </c>
       <c r="X6">
         <v>0.4270509137827634</v>
@@ -1673,16 +1673,16 @@
         <v>0.3052890151364571</v>
       </c>
       <c r="AN6">
-        <v>-0.1408601764411822</v>
+        <v>-0.1408601764411823</v>
       </c>
       <c r="AO6">
-        <v>-0.06294638134902261</v>
+        <v>-0.06294638134902258</v>
       </c>
       <c r="AP6">
-        <v>-0.08617993521812582</v>
+        <v>-0.08617993521812584</v>
       </c>
       <c r="AQ6">
-        <v>0.06918864330727771</v>
+        <v>0.06918864330727774</v>
       </c>
       <c r="AR6">
         <v>0.6471336984139858</v>
@@ -1706,10 +1706,10 @@
         <v>-0.2011783881441936</v>
       </c>
       <c r="AY6">
-        <v>-0.05361650610630309</v>
+        <v>-0.05361650610630308</v>
       </c>
       <c r="AZ6">
-        <v>-0.03106671980222752</v>
+        <v>-0.03106671980222751</v>
       </c>
       <c r="BA6">
         <v>0.2767439225737506</v>
@@ -1736,7 +1736,7 @@
         <v>0.2602454537886317</v>
       </c>
       <c r="BI6">
-        <v>0.005968783171217401</v>
+        <v>0.005968783171217395</v>
       </c>
       <c r="BJ6">
         <v>0.2908826155483171</v>
@@ -1748,13 +1748,13 @@
         <v>0.1071558186950637</v>
       </c>
       <c r="BM6">
-        <v>0.4928148042656748</v>
+        <v>0.4928148042656749</v>
       </c>
       <c r="BN6">
         <v>-0.271098288959836</v>
       </c>
       <c r="BO6">
-        <v>-0.002881243690523026</v>
+        <v>-0.002881243690523003</v>
       </c>
       <c r="BP6">
         <v>-0.1168930777463223</v>
@@ -1786,10 +1786,10 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>0.09852372064549439</v>
+        <v>0.09852372064549436</v>
       </c>
       <c r="H7">
-        <v>0.3322466879451833</v>
+        <v>0.3322466879451832</v>
       </c>
       <c r="I7">
         <v>0.2056483470306451</v>
@@ -1813,7 +1813,7 @@
         <v>0.5175530583329074</v>
       </c>
       <c r="P7">
-        <v>0.3797040398241226</v>
+        <v>0.3797040398241227</v>
       </c>
       <c r="Q7">
         <v>0.6337775180682088</v>
@@ -1843,10 +1843,10 @@
         <v>0.4534277500687597</v>
       </c>
       <c r="Z7">
-        <v>0.09377794132571458</v>
+        <v>0.0937779413257146</v>
       </c>
       <c r="AA7">
-        <v>0.2856433804644709</v>
+        <v>0.285643380464471</v>
       </c>
       <c r="AB7">
         <v>0.1040747678041318</v>
@@ -1894,22 +1894,22 @@
         <v>-0.3176735834889085</v>
       </c>
       <c r="AQ7">
-        <v>-0.02945399502968301</v>
+        <v>-0.029453995029683</v>
       </c>
       <c r="AR7">
-        <v>0.2794598291751212</v>
+        <v>0.2794598291751213</v>
       </c>
       <c r="AS7">
         <v>0.1715784838039659</v>
       </c>
       <c r="AT7">
-        <v>0.6990709181809003</v>
+        <v>0.6990709181809004</v>
       </c>
       <c r="AU7">
         <v>-0.5516781103030769</v>
       </c>
       <c r="AV7">
-        <v>-0.0373538028290351</v>
+        <v>-0.03735380282903509</v>
       </c>
       <c r="AW7">
         <v>0.6914189501907738</v>
@@ -1945,7 +1945,7 @@
         <v>0.5878422382228842</v>
       </c>
       <c r="BH7">
-        <v>0.491712763457485</v>
+        <v>0.4917127634574851</v>
       </c>
       <c r="BI7">
         <v>-0.1651947968585291</v>
@@ -1972,18 +1972,18 @@
         <v>-0.4796485521289377</v>
       </c>
       <c r="BQ7">
-        <v>0.06875546642267573</v>
+        <v>0.06875546642267574</v>
       </c>
       <c r="BR7">
-        <v>0.1926508084556657</v>
+        <v>0.1926508084556656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>-0.07647180455298133</v>
+        <v>-0.07647180455298136</v>
       </c>
       <c r="B8">
-        <v>0.06697000637624108</v>
+        <v>0.06697000637624109</v>
       </c>
       <c r="C8">
         <v>0.2497391574718832</v>
@@ -1992,10 +1992,10 @@
         <v>0.1863380039150494</v>
       </c>
       <c r="E8">
-        <v>0.04417786151219624</v>
+        <v>0.04417786151219623</v>
       </c>
       <c r="F8">
-        <v>0.09852372064549439</v>
+        <v>0.09852372064549436</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>0.4858577744140417</v>
       </c>
       <c r="I8">
-        <v>0.3005912364919943</v>
+        <v>0.3005912364919942</v>
       </c>
       <c r="J8">
         <v>0.3216688391516814</v>
@@ -2013,13 +2013,13 @@
         <v>0.3163894599691452</v>
       </c>
       <c r="L8">
-        <v>0.08051863651885148</v>
+        <v>0.08051863651885145</v>
       </c>
       <c r="M8">
         <v>0.2826793251572536</v>
       </c>
       <c r="N8">
-        <v>-0.01490681820359155</v>
+        <v>-0.01490681820359154</v>
       </c>
       <c r="O8">
         <v>0.05612059693361727</v>
@@ -2028,31 +2028,31 @@
         <v>0.2038441813170739</v>
       </c>
       <c r="Q8">
-        <v>0.1780829562339614</v>
+        <v>0.1780829562339613</v>
       </c>
       <c r="R8">
         <v>0.2254183312510533</v>
       </c>
       <c r="S8">
-        <v>0.2867880056649192</v>
+        <v>0.2867880056649191</v>
       </c>
       <c r="T8">
-        <v>0.05175875497351325</v>
+        <v>0.05175875497351324</v>
       </c>
       <c r="U8">
-        <v>-0.04065188940373561</v>
+        <v>-0.04065188940373562</v>
       </c>
       <c r="V8">
         <v>0.1039482860986943</v>
       </c>
       <c r="W8">
-        <v>0.1629002712338486</v>
+        <v>0.1629002712338485</v>
       </c>
       <c r="X8">
-        <v>0.0168276070000573</v>
+        <v>0.01682760700005729</v>
       </c>
       <c r="Y8">
-        <v>0.04726366986913484</v>
+        <v>0.04726366986913481</v>
       </c>
       <c r="Z8">
         <v>0.3722087524418143</v>
@@ -2064,7 +2064,7 @@
         <v>0.2480980731299828</v>
       </c>
       <c r="AC8">
-        <v>0.3981327316467003</v>
+        <v>0.3981327316467002</v>
       </c>
       <c r="AD8">
         <v>0.1548837425855292</v>
@@ -2088,19 +2088,19 @@
         <v>0.2014262228032714</v>
       </c>
       <c r="AK8">
-        <v>0.07594167062982217</v>
+        <v>0.07594167062982214</v>
       </c>
       <c r="AL8">
         <v>0.3547144035906181</v>
       </c>
       <c r="AM8">
-        <v>0.05007678765066133</v>
+        <v>0.05007678765066136</v>
       </c>
       <c r="AN8">
         <v>0.5359134371679464</v>
       </c>
       <c r="AO8">
-        <v>-0.02657441326273877</v>
+        <v>-0.02657441326273876</v>
       </c>
       <c r="AP8">
         <v>0.1731964102869479</v>
@@ -2109,16 +2109,16 @@
         <v>0.1712458286357201</v>
       </c>
       <c r="AR8">
-        <v>0.03332074660277219</v>
+        <v>0.0333207466027722</v>
       </c>
       <c r="AS8">
         <v>0.2995418833132182</v>
       </c>
       <c r="AT8">
-        <v>-0.02395491118527681</v>
+        <v>-0.02395491118527684</v>
       </c>
       <c r="AU8">
-        <v>0.09675982119206325</v>
+        <v>0.09675982119206326</v>
       </c>
       <c r="AV8">
         <v>0.3272342425022901</v>
@@ -2130,10 +2130,10 @@
         <v>0.3210306255251907</v>
       </c>
       <c r="AY8">
-        <v>0.08924119149508909</v>
+        <v>0.08924119149508908</v>
       </c>
       <c r="AZ8">
-        <v>-0.01224287983443979</v>
+        <v>-0.01224287983443975</v>
       </c>
       <c r="BA8">
         <v>0.1300341151349338</v>
@@ -2148,10 +2148,10 @@
         <v>0.7046839607401914</v>
       </c>
       <c r="BE8">
-        <v>0.2839764569752609</v>
+        <v>0.2839764569752608</v>
       </c>
       <c r="BF8">
-        <v>0.1063799217300708</v>
+        <v>0.1063799217300707</v>
       </c>
       <c r="BG8">
         <v>0.1780424289057974</v>
@@ -2160,16 +2160,16 @@
         <v>0.1575919130509088</v>
       </c>
       <c r="BI8">
-        <v>0.01923911953388723</v>
+        <v>0.01923911953388722</v>
       </c>
       <c r="BJ8">
-        <v>0.3307968423322505</v>
+        <v>0.3307968423322504</v>
       </c>
       <c r="BK8">
         <v>0.08201474185828246</v>
       </c>
       <c r="BL8">
-        <v>0.1262985819990905</v>
+        <v>0.1262985819990906</v>
       </c>
       <c r="BM8">
         <v>0.1028547210381896</v>
@@ -2178,10 +2178,10 @@
         <v>0.4856033476671952</v>
       </c>
       <c r="BO8">
-        <v>0.008432696919855969</v>
+        <v>0.008432696919855954</v>
       </c>
       <c r="BP8">
-        <v>0.09491221966426862</v>
+        <v>0.09491221966426865</v>
       </c>
       <c r="BQ8">
         <v>0.244995882875642</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.01563934308344956</v>
+        <v>0.01563934308344957</v>
       </c>
       <c r="B9">
         <v>0.3971324896415877</v>
@@ -2207,7 +2207,7 @@
         <v>0.3470997648761921</v>
       </c>
       <c r="F9">
-        <v>0.3322466879451833</v>
+        <v>0.3322466879451832</v>
       </c>
       <c r="G9">
         <v>0.4858577744140417</v>
@@ -2222,7 +2222,7 @@
         <v>0.5867841025640934</v>
       </c>
       <c r="K9">
-        <v>0.3301837940174211</v>
+        <v>0.330183794017421</v>
       </c>
       <c r="L9">
         <v>0.2131870480656162</v>
@@ -2231,7 +2231,7 @@
         <v>0.3909010305964913</v>
       </c>
       <c r="N9">
-        <v>0.01512497877923543</v>
+        <v>0.01512497877923542</v>
       </c>
       <c r="O9">
         <v>0.1310005957823311</v>
@@ -2243,13 +2243,13 @@
         <v>0.2886977392842954</v>
       </c>
       <c r="R9">
-        <v>0.1073348257594222</v>
+        <v>0.1073348257594221</v>
       </c>
       <c r="S9">
         <v>0.3190849431210687</v>
       </c>
       <c r="T9">
-        <v>0.07711563041555274</v>
+        <v>0.07711563041555272</v>
       </c>
       <c r="U9">
         <v>0.1587531572739671</v>
@@ -2279,7 +2279,7 @@
         <v>0.3930601617098071</v>
       </c>
       <c r="AD9">
-        <v>0.3945263109294574</v>
+        <v>0.3945263109294575</v>
       </c>
       <c r="AE9">
         <v>0.3288142634917523</v>
@@ -2288,13 +2288,13 @@
         <v>0.4087570467695326</v>
       </c>
       <c r="AG9">
-        <v>0.4185676757337321</v>
+        <v>0.418567675733732</v>
       </c>
       <c r="AH9">
         <v>0.5619941262396704</v>
       </c>
       <c r="AI9">
-        <v>0.7824173238569316</v>
+        <v>0.7824173238569315</v>
       </c>
       <c r="AJ9">
         <v>0.2769467987643239</v>
@@ -2312,10 +2312,10 @@
         <v>0.2978100884272263</v>
       </c>
       <c r="AO9">
-        <v>-0.07356233600256593</v>
+        <v>-0.07356233600256591</v>
       </c>
       <c r="AP9">
-        <v>-0.006998604390283237</v>
+        <v>-0.006998604390283248</v>
       </c>
       <c r="AQ9">
         <v>0.1353233426967667</v>
@@ -2333,10 +2333,10 @@
         <v>-0.2421385332059808</v>
       </c>
       <c r="AV9">
-        <v>0.2343859166090143</v>
+        <v>0.2343859166090144</v>
       </c>
       <c r="AW9">
-        <v>0.4093770498169907</v>
+        <v>0.4093770498169906</v>
       </c>
       <c r="AX9">
         <v>0.3179043065530517</v>
@@ -2360,19 +2360,19 @@
         <v>0.5722119348828764</v>
       </c>
       <c r="BE9">
-        <v>0.1812716594129277</v>
+        <v>0.1812716594129276</v>
       </c>
       <c r="BF9">
         <v>0.2567805245780702</v>
       </c>
       <c r="BG9">
-        <v>0.418144557408371</v>
+        <v>0.4181445574083709</v>
       </c>
       <c r="BH9">
         <v>0.2607321665253585</v>
       </c>
       <c r="BI9">
-        <v>-0.02380478319921953</v>
+        <v>-0.02380478319921954</v>
       </c>
       <c r="BJ9">
         <v>0.3205191477931733</v>
@@ -2381,7 +2381,7 @@
         <v>-0.1100259527142302</v>
       </c>
       <c r="BL9">
-        <v>0.09039673152432014</v>
+        <v>0.09039673152432016</v>
       </c>
       <c r="BM9">
         <v>0.4861899489125276</v>
@@ -2390,24 +2390,24 @@
         <v>0.3651771320829576</v>
       </c>
       <c r="BO9">
-        <v>0.05067950120329013</v>
+        <v>0.05067950120329014</v>
       </c>
       <c r="BP9">
         <v>-0.1489923025737508</v>
       </c>
       <c r="BQ9">
-        <v>0.2925884938953603</v>
+        <v>0.2925884938953604</v>
       </c>
       <c r="BR9">
-        <v>0.02349517145619149</v>
+        <v>0.02349517145619151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>-0.004203715761054981</v>
+        <v>-0.004203715761054987</v>
       </c>
       <c r="B10">
-        <v>0.09412086861154725</v>
+        <v>0.09412086861154727</v>
       </c>
       <c r="C10">
         <v>0.3146390491452887</v>
@@ -2416,13 +2416,13 @@
         <v>0.2989613432939284</v>
       </c>
       <c r="E10">
-        <v>-0.02163827414123358</v>
+        <v>-0.0216382741412336</v>
       </c>
       <c r="F10">
         <v>0.2056483470306451</v>
       </c>
       <c r="G10">
-        <v>0.3005912364919943</v>
+        <v>0.3005912364919942</v>
       </c>
       <c r="H10">
         <v>0.4113611993729605</v>
@@ -2440,28 +2440,28 @@
         <v>0.1588136625496389</v>
       </c>
       <c r="M10">
-        <v>0.1644161577365441</v>
+        <v>0.164416157736544</v>
       </c>
       <c r="N10">
-        <v>0.02791479113335502</v>
+        <v>0.027914791133355</v>
       </c>
       <c r="O10">
-        <v>0.03976522127399601</v>
+        <v>0.03976522127399603</v>
       </c>
       <c r="P10">
-        <v>0.003175257987240059</v>
+        <v>0.00317525798724006</v>
       </c>
       <c r="Q10">
-        <v>0.02816029602196699</v>
+        <v>0.02816029602196696</v>
       </c>
       <c r="R10">
         <v>0.1432567549593635</v>
       </c>
       <c r="S10">
-        <v>0.1458067516771154</v>
+        <v>0.1458067516771153</v>
       </c>
       <c r="T10">
-        <v>0.07877497873776193</v>
+        <v>0.07877497873776194</v>
       </c>
       <c r="U10">
         <v>0.2481469840586732</v>
@@ -2479,7 +2479,7 @@
         <v>0.1687968691910274</v>
       </c>
       <c r="Z10">
-        <v>0.1056684750221368</v>
+        <v>0.1056684750221367</v>
       </c>
       <c r="AA10">
         <v>0.1967795794512676</v>
@@ -2494,7 +2494,7 @@
         <v>0.1995233880796284</v>
       </c>
       <c r="AE10">
-        <v>0.07874373883352849</v>
+        <v>0.07874373883352848</v>
       </c>
       <c r="AF10">
         <v>0.1901602145589499</v>
@@ -2530,22 +2530,22 @@
         <v>-0.1865325626653916</v>
       </c>
       <c r="AQ10">
-        <v>0.07990970319665273</v>
+        <v>0.07990970319665272</v>
       </c>
       <c r="AR10">
-        <v>0.06218014448839663</v>
+        <v>0.0621801444883966</v>
       </c>
       <c r="AS10">
         <v>0.3470169844228255</v>
       </c>
       <c r="AT10">
-        <v>0.08148932196101265</v>
+        <v>0.08148932196101262</v>
       </c>
       <c r="AU10">
         <v>-0.2825567873669685</v>
       </c>
       <c r="AV10">
-        <v>0.04354670782699682</v>
+        <v>0.04354670782699681</v>
       </c>
       <c r="AW10">
         <v>0.2539707476851705</v>
@@ -2554,7 +2554,7 @@
         <v>0.6701391996767447</v>
       </c>
       <c r="AY10">
-        <v>0.03588544089295026</v>
+        <v>0.03588544089295023</v>
       </c>
       <c r="AZ10">
         <v>-0.3334654330217837</v>
@@ -2566,16 +2566,16 @@
         <v>0.1952737668111877</v>
       </c>
       <c r="BC10">
-        <v>0.1133503853564954</v>
+        <v>0.1133503853564953</v>
       </c>
       <c r="BD10">
         <v>0.3427707996397156</v>
       </c>
       <c r="BE10">
-        <v>0.02414658646128147</v>
+        <v>0.02414658646128145</v>
       </c>
       <c r="BF10">
-        <v>0.03873160958281665</v>
+        <v>0.03873160958281661</v>
       </c>
       <c r="BG10">
         <v>0.1572785142159224</v>
@@ -2593,16 +2593,16 @@
         <v>-0.1398779783691476</v>
       </c>
       <c r="BL10">
-        <v>-0.06110322876470808</v>
+        <v>-0.06110322876470806</v>
       </c>
       <c r="BM10">
-        <v>0.2322623071465211</v>
+        <v>0.232262307146521</v>
       </c>
       <c r="BN10">
         <v>0.5931847042371626</v>
       </c>
       <c r="BO10">
-        <v>-0.007052858075198342</v>
+        <v>-0.007052858075198376</v>
       </c>
       <c r="BP10">
         <v>-0.3091853760733724</v>
@@ -2611,7 +2611,7 @@
         <v>0.1109872817975772</v>
       </c>
       <c r="BR10">
-        <v>-0.004119863853618199</v>
+        <v>-0.004119863853618197</v>
       </c>
     </row>
     <row r="11">
@@ -2649,7 +2649,7 @@
         <v>0.3603737833097832</v>
       </c>
       <c r="L11">
-        <v>0.4149864767046605</v>
+        <v>0.4149864767046606</v>
       </c>
       <c r="M11">
         <v>0.3855776885031645</v>
@@ -2676,7 +2676,7 @@
         <v>0.2764290725187684</v>
       </c>
       <c r="U11">
-        <v>0.1992659193635914</v>
+        <v>0.1992659193635913</v>
       </c>
       <c r="V11">
         <v>0.3283765803775496</v>
@@ -2712,7 +2712,7 @@
         <v>0.2196616999330845</v>
       </c>
       <c r="AG11">
-        <v>0.4704768313232849</v>
+        <v>0.4704768313232848</v>
       </c>
       <c r="AH11">
         <v>0.5116686621849907</v>
@@ -2733,16 +2733,16 @@
         <v>0.3239071411455954</v>
       </c>
       <c r="AN11">
-        <v>0.2141468706699332</v>
+        <v>0.2141468706699333</v>
       </c>
       <c r="AO11">
         <v>0.06715600735259596</v>
       </c>
       <c r="AP11">
-        <v>-0.07912030969390711</v>
+        <v>-0.07912030969390708</v>
       </c>
       <c r="AQ11">
-        <v>0.06302232280880848</v>
+        <v>0.06302232280880846</v>
       </c>
       <c r="AR11">
         <v>0.2384225514466057</v>
@@ -2772,13 +2772,13 @@
         <v>-0.2090881636179694</v>
       </c>
       <c r="BA11">
-        <v>0.2381776426920908</v>
+        <v>0.2381776426920907</v>
       </c>
       <c r="BB11">
         <v>0.2833130791438622</v>
       </c>
       <c r="BC11">
-        <v>0.2817079303319186</v>
+        <v>0.2817079303319185</v>
       </c>
       <c r="BD11">
         <v>0.457540613560643</v>
@@ -2820,15 +2820,15 @@
         <v>-0.199667786962586</v>
       </c>
       <c r="BQ11">
-        <v>0.1632746283646629</v>
+        <v>0.1632746283646628</v>
       </c>
       <c r="BR11">
-        <v>0.02411196686783855</v>
+        <v>0.02411196686783851</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.07645635761104071</v>
+        <v>0.07645635761104069</v>
       </c>
       <c r="B12">
         <v>0.2413315776240654</v>
@@ -2849,7 +2849,7 @@
         <v>0.3163894599691452</v>
       </c>
       <c r="H12">
-        <v>0.3301837940174211</v>
+        <v>0.330183794017421</v>
       </c>
       <c r="I12">
         <v>0.3116058413482813</v>
@@ -2870,10 +2870,10 @@
         <v>0.1148763838101424</v>
       </c>
       <c r="O12">
-        <v>0.2463608473097969</v>
+        <v>0.2463608473097968</v>
       </c>
       <c r="P12">
-        <v>0.3592134517946254</v>
+        <v>0.3592134517946253</v>
       </c>
       <c r="Q12">
         <v>0.3232370856734174</v>
@@ -2897,7 +2897,7 @@
         <v>0.1830938100409912</v>
       </c>
       <c r="X12">
-        <v>0.2519458645445983</v>
+        <v>0.2519458645445982</v>
       </c>
       <c r="Y12">
         <v>0.3398889389343406</v>
@@ -2942,16 +2942,16 @@
         <v>0.2874761279372723</v>
       </c>
       <c r="AM12">
-        <v>0.1864148687122232</v>
+        <v>0.1864148687122231</v>
       </c>
       <c r="AN12">
         <v>0.2756260663158595</v>
       </c>
       <c r="AO12">
-        <v>0.1128052291875371</v>
+        <v>0.112805229187537</v>
       </c>
       <c r="AP12">
-        <v>-0.05768547851937358</v>
+        <v>-0.05768547851937354</v>
       </c>
       <c r="AQ12">
         <v>0.2000226096475824</v>
@@ -2978,10 +2978,10 @@
         <v>0.2988742152497418</v>
       </c>
       <c r="AY12">
-        <v>0.3261366270908865</v>
+        <v>0.3261366270908864</v>
       </c>
       <c r="AZ12">
-        <v>-0.2299103931914541</v>
+        <v>-0.229910393191454</v>
       </c>
       <c r="BA12">
         <v>0.2161715738415062</v>
@@ -2999,7 +2999,7 @@
         <v>0.2858676413363211</v>
       </c>
       <c r="BF12">
-        <v>0.384582580708385</v>
+        <v>0.3845825807083849</v>
       </c>
       <c r="BG12">
         <v>0.4026684006384572</v>
@@ -3008,7 +3008,7 @@
         <v>0.3371603254621376</v>
       </c>
       <c r="BI12">
-        <v>-0.02996769418967704</v>
+        <v>-0.02996769418967705</v>
       </c>
       <c r="BJ12">
         <v>0.2386873527495568</v>
@@ -3029,13 +3029,13 @@
         <v>0.277332648013525</v>
       </c>
       <c r="BP12">
-        <v>-0.1868564435155315</v>
+        <v>-0.1868564435155314</v>
       </c>
       <c r="BQ12">
         <v>0.2305187818356912</v>
       </c>
       <c r="BR12">
-        <v>-0.06186906461447747</v>
+        <v>-0.06186906461447744</v>
       </c>
     </row>
     <row r="13">
@@ -3058,7 +3058,7 @@
         <v>0.7396410405202027</v>
       </c>
       <c r="G13">
-        <v>0.08051863651885148</v>
+        <v>0.08051863651885145</v>
       </c>
       <c r="H13">
         <v>0.2131870480656162</v>
@@ -3067,7 +3067,7 @@
         <v>0.1588136625496389</v>
       </c>
       <c r="J13">
-        <v>0.4149864767046605</v>
+        <v>0.4149864767046606</v>
       </c>
       <c r="K13">
         <v>0.3160857488019226</v>
@@ -3109,28 +3109,28 @@
         <v>0.2288227057413856</v>
       </c>
       <c r="X13">
-        <v>0.3968034444773813</v>
+        <v>0.3968034444773812</v>
       </c>
       <c r="Y13">
         <v>0.4987914001347437</v>
       </c>
       <c r="Z13">
-        <v>-0.04322159410190252</v>
+        <v>-0.04322159410190254</v>
       </c>
       <c r="AA13">
         <v>0.1584229328868029</v>
       </c>
       <c r="AB13">
-        <v>-0.001469485171316012</v>
+        <v>-0.001469485171316037</v>
       </c>
       <c r="AC13">
-        <v>0.06638678206477679</v>
+        <v>0.06638678206477677</v>
       </c>
       <c r="AD13">
         <v>0.3468736854470864</v>
       </c>
       <c r="AE13">
-        <v>0.3875480515633799</v>
+        <v>0.3875480515633798</v>
       </c>
       <c r="AF13">
         <v>0.1098370122353853</v>
@@ -3166,7 +3166,7 @@
         <v>-0.2615369961821907</v>
       </c>
       <c r="AQ13">
-        <v>-0.07110016303754101</v>
+        <v>-0.07110016303754103</v>
       </c>
       <c r="AR13">
         <v>0.2020568857975557</v>
@@ -3196,7 +3196,7 @@
         <v>-0.3608050487313455</v>
       </c>
       <c r="BA13">
-        <v>0.09293590569513338</v>
+        <v>0.09293590569513335</v>
       </c>
       <c r="BB13">
         <v>0.1818625122682776</v>
@@ -3217,13 +3217,13 @@
         <v>0.4494679966540501</v>
       </c>
       <c r="BH13">
-        <v>0.4946887115785982</v>
+        <v>0.4946887115785983</v>
       </c>
       <c r="BI13">
         <v>-0.1432419614880656</v>
       </c>
       <c r="BJ13">
-        <v>0.06113020842194036</v>
+        <v>0.06113020842194034</v>
       </c>
       <c r="BK13">
         <v>-0.2250106838536242</v>
@@ -3244,7 +3244,7 @@
         <v>-0.4014058711894786</v>
       </c>
       <c r="BQ13">
-        <v>-0.03405685371166332</v>
+        <v>-0.03405685371166334</v>
       </c>
       <c r="BR13">
         <v>0.08558497084893145</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.1715824180361433</v>
+        <v>0.1715824180361434</v>
       </c>
       <c r="B14">
         <v>0.3651778223942292</v>
@@ -3276,7 +3276,7 @@
         <v>0.3909010305964913</v>
       </c>
       <c r="I14">
-        <v>0.1644161577365441</v>
+        <v>0.164416157736544</v>
       </c>
       <c r="J14">
         <v>0.3855776885031645</v>
@@ -3291,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="N14">
-        <v>0.3003393057104792</v>
+        <v>0.3003393057104793</v>
       </c>
       <c r="O14">
         <v>0.5167545530487645</v>
@@ -3330,10 +3330,10 @@
         <v>0.1596041801268009</v>
       </c>
       <c r="AA14">
-        <v>0.1298318335949169</v>
+        <v>0.1298318335949168</v>
       </c>
       <c r="AB14">
-        <v>0.05247257347428654</v>
+        <v>0.05247257347428656</v>
       </c>
       <c r="AC14">
         <v>0.2305744947426143</v>
@@ -3369,16 +3369,16 @@
         <v>0.1691371912403196</v>
       </c>
       <c r="AN14">
-        <v>0.1951875826103697</v>
+        <v>0.1951875826103696</v>
       </c>
       <c r="AO14">
         <v>0.3313034923290459</v>
       </c>
       <c r="AP14">
-        <v>-0.02793787257067175</v>
+        <v>-0.02793787257067176</v>
       </c>
       <c r="AQ14">
-        <v>0.01415313972759976</v>
+        <v>0.01415313972759977</v>
       </c>
       <c r="AR14">
         <v>0.2875543737046246</v>
@@ -3390,7 +3390,7 @@
         <v>0.538999459870001</v>
       </c>
       <c r="AU14">
-        <v>-0.2652900877362808</v>
+        <v>-0.2652900877362809</v>
       </c>
       <c r="AV14">
         <v>0.07324775693792404</v>
@@ -3399,13 +3399,13 @@
         <v>0.282677396225624</v>
       </c>
       <c r="AX14">
-        <v>0.1747250605082012</v>
+        <v>0.1747250605082011</v>
       </c>
       <c r="AY14">
         <v>0.584269606329313</v>
       </c>
       <c r="AZ14">
-        <v>-0.2481372684173339</v>
+        <v>-0.248137268417334</v>
       </c>
       <c r="BA14">
         <v>0.1076745656347624</v>
@@ -3432,7 +3432,7 @@
         <v>0.4075905980047503</v>
       </c>
       <c r="BI14">
-        <v>0.00323084973881806</v>
+        <v>0.003230849738818055</v>
       </c>
       <c r="BJ14">
         <v>0.1935939764012155</v>
@@ -3447,48 +3447,48 @@
         <v>0.3062480564408996</v>
       </c>
       <c r="BN14">
-        <v>0.272987054290026</v>
+        <v>0.2729870542900259</v>
       </c>
       <c r="BO14">
-        <v>0.5589902434566772</v>
+        <v>0.5589902434566774</v>
       </c>
       <c r="BP14">
-        <v>-0.2131897885463789</v>
+        <v>-0.213189788546379</v>
       </c>
       <c r="BQ14">
-        <v>0.0741011234371247</v>
+        <v>0.07410112343712472</v>
       </c>
       <c r="BR14">
-        <v>-0.0428193697066622</v>
+        <v>-0.04281936970666218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.08859376413208347</v>
+        <v>0.08859376413208346</v>
       </c>
       <c r="B15">
-        <v>0.07840112940071385</v>
+        <v>0.07840112940071386</v>
       </c>
       <c r="C15">
-        <v>0.09108327508859106</v>
+        <v>0.09108327508859104</v>
       </c>
       <c r="D15">
         <v>0.01588767646759677</v>
       </c>
       <c r="E15">
-        <v>-0.01872291362013562</v>
+        <v>-0.01872291362013559</v>
       </c>
       <c r="F15">
         <v>0.3525352269844746</v>
       </c>
       <c r="G15">
-        <v>-0.01490681820359155</v>
+        <v>-0.01490681820359154</v>
       </c>
       <c r="H15">
-        <v>0.01512497877923543</v>
+        <v>0.01512497877923542</v>
       </c>
       <c r="I15">
-        <v>0.02791479113335502</v>
+        <v>0.027914791133355</v>
       </c>
       <c r="J15">
         <v>0.1492705526812321</v>
@@ -3500,7 +3500,7 @@
         <v>0.4442350727872413</v>
       </c>
       <c r="M15">
-        <v>0.3003393057104792</v>
+        <v>0.3003393057104793</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -3509,7 +3509,7 @@
         <v>0.4951637780409809</v>
       </c>
       <c r="P15">
-        <v>0.4025369256874655</v>
+        <v>0.4025369256874654</v>
       </c>
       <c r="Q15">
         <v>0.243057130532955</v>
@@ -3527,7 +3527,7 @@
         <v>0.2044706750690851</v>
       </c>
       <c r="V15">
-        <v>0.09485941173305443</v>
+        <v>0.09485941173305441</v>
       </c>
       <c r="W15">
         <v>0.1508920821087588</v>
@@ -3545,19 +3545,19 @@
         <v>-0.01628903088772804</v>
       </c>
       <c r="AB15">
-        <v>-0.0237594098647113</v>
+        <v>-0.02375940986471131</v>
       </c>
       <c r="AC15">
-        <v>0.03502764141135334</v>
+        <v>0.03502764141135333</v>
       </c>
       <c r="AD15">
-        <v>0.05752910517912828</v>
+        <v>0.05752910517912827</v>
       </c>
       <c r="AE15">
         <v>0.1608692399040982</v>
       </c>
       <c r="AF15">
-        <v>-0.02988232081870757</v>
+        <v>-0.02988232081870758</v>
       </c>
       <c r="AG15">
         <v>0.1396476264734156</v>
@@ -3593,7 +3593,7 @@
         <v>-0.04432232851642876</v>
       </c>
       <c r="AR15">
-        <v>0.0565510457981351</v>
+        <v>0.05655104579813511</v>
       </c>
       <c r="AS15">
         <v>0.1731576916349824</v>
@@ -3617,13 +3617,13 @@
         <v>0.4739652871579609</v>
       </c>
       <c r="AZ15">
-        <v>-0.2098012047863404</v>
+        <v>-0.2098012047863405</v>
       </c>
       <c r="BA15">
         <v>-0.07331576687296533</v>
       </c>
       <c r="BB15">
-        <v>0.05185979565942452</v>
+        <v>0.05185979565942453</v>
       </c>
       <c r="BC15">
         <v>0.2024489152647979</v>
@@ -3644,7 +3644,7 @@
         <v>0.1086459755745335</v>
       </c>
       <c r="BI15">
-        <v>0.007790922999669946</v>
+        <v>0.007790922999669953</v>
       </c>
       <c r="BJ15">
         <v>-0.05896414389556855</v>
@@ -3656,7 +3656,7 @@
         <v>-0.1903464562118386</v>
       </c>
       <c r="BM15">
-        <v>0.07272273261731013</v>
+        <v>0.07272273261731015</v>
       </c>
       <c r="BN15">
         <v>0.1073152491493141</v>
@@ -3668,7 +3668,7 @@
         <v>-0.1789698023885791</v>
       </c>
       <c r="BQ15">
-        <v>-0.09147567502842688</v>
+        <v>-0.09147567502842689</v>
       </c>
       <c r="BR15">
         <v>0.03967907082894034</v>
@@ -3685,10 +3685,10 @@
         <v>0.2063988744233315</v>
       </c>
       <c r="D16">
-        <v>0.1804994414204048</v>
+        <v>0.1804994414204049</v>
       </c>
       <c r="E16">
-        <v>0.08612642912216581</v>
+        <v>0.08612642912216582</v>
       </c>
       <c r="F16">
         <v>0.5175530583329074</v>
@@ -3700,13 +3700,13 @@
         <v>0.1310005957823311</v>
       </c>
       <c r="I16">
-        <v>0.03976522127399601</v>
+        <v>0.03976522127399603</v>
       </c>
       <c r="J16">
         <v>0.3179751862886454</v>
       </c>
       <c r="K16">
-        <v>0.2463608473097969</v>
+        <v>0.2463608473097968</v>
       </c>
       <c r="L16">
         <v>0.6673745521335608</v>
@@ -3742,7 +3742,7 @@
         <v>0.185110901762722</v>
       </c>
       <c r="W16">
-        <v>0.1498428071906256</v>
+        <v>0.1498428071906257</v>
       </c>
       <c r="X16">
         <v>0.2607027875350448</v>
@@ -3751,13 +3751,13 @@
         <v>0.4229477451527646</v>
       </c>
       <c r="Z16">
-        <v>-0.06335395718497462</v>
+        <v>-0.06335395718497461</v>
       </c>
       <c r="AA16">
-        <v>0.01970248164625295</v>
+        <v>0.01970248164625297</v>
       </c>
       <c r="AB16">
-        <v>-0.04553184283102019</v>
+        <v>-0.04553184283102017</v>
       </c>
       <c r="AC16">
         <v>0.03775911288614336</v>
@@ -3787,13 +3787,13 @@
         <v>0.3153128854410476</v>
       </c>
       <c r="AL16">
-        <v>0.02631463070978511</v>
+        <v>0.02631463070978512</v>
       </c>
       <c r="AM16">
-        <v>0.09563100436652007</v>
+        <v>0.09563100436652008</v>
       </c>
       <c r="AN16">
-        <v>0.07966906951694713</v>
+        <v>0.07966906951694715</v>
       </c>
       <c r="AO16">
         <v>0.516363842997219</v>
@@ -3832,7 +3832,7 @@
         <v>-0.2354593042501343</v>
       </c>
       <c r="BA16">
-        <v>-0.02363372459415723</v>
+        <v>-0.0236337245941572</v>
       </c>
       <c r="BB16">
         <v>0.1768154293616226</v>
@@ -3856,10 +3856,10 @@
         <v>0.3815670765630684</v>
       </c>
       <c r="BI16">
-        <v>-0.08283697910961772</v>
+        <v>-0.08283697910961774</v>
       </c>
       <c r="BJ16">
-        <v>-0.03692313850820914</v>
+        <v>-0.03692313850820912</v>
       </c>
       <c r="BK16">
         <v>-0.1674433039551061</v>
@@ -3880,7 +3880,7 @@
         <v>-0.2165179904061903</v>
       </c>
       <c r="BQ16">
-        <v>-0.1137884659488672</v>
+        <v>-0.1137884659488671</v>
       </c>
       <c r="BR16">
         <v>0.0300687360012118</v>
@@ -3897,13 +3897,13 @@
         <v>0.2046087762975946</v>
       </c>
       <c r="D17">
-        <v>0.2511679338560774</v>
+        <v>0.2511679338560775</v>
       </c>
       <c r="E17">
         <v>0.2727355779648076</v>
       </c>
       <c r="F17">
-        <v>0.3797040398241226</v>
+        <v>0.3797040398241227</v>
       </c>
       <c r="G17">
         <v>0.2038441813170739</v>
@@ -3912,13 +3912,13 @@
         <v>0.2875855799661172</v>
       </c>
       <c r="I17">
-        <v>0.003175257987240059</v>
+        <v>0.00317525798724006</v>
       </c>
       <c r="J17">
         <v>0.3619656164027702</v>
       </c>
       <c r="K17">
-        <v>0.3592134517946254</v>
+        <v>0.3592134517946253</v>
       </c>
       <c r="L17">
         <v>0.5017823980219823</v>
@@ -3927,7 +3927,7 @@
         <v>0.5462112175820257</v>
       </c>
       <c r="N17">
-        <v>0.4025369256874655</v>
+        <v>0.4025369256874654</v>
       </c>
       <c r="O17">
         <v>0.4484184199564797</v>
@@ -4002,16 +4002,16 @@
         <v>0.3286231914362282</v>
       </c>
       <c r="AM17">
-        <v>0.06375690611788008</v>
+        <v>0.0637569061178801</v>
       </c>
       <c r="AN17">
         <v>0.1629625193673907</v>
       </c>
       <c r="AO17">
-        <v>0.4158137120622744</v>
+        <v>0.4158137120622743</v>
       </c>
       <c r="AP17">
-        <v>0.03675417648683978</v>
+        <v>0.03675417648683979</v>
       </c>
       <c r="AQ17">
         <v>0.1206436208575783</v>
@@ -4032,13 +4032,13 @@
         <v>0.1415720823675534</v>
       </c>
       <c r="AW17">
-        <v>0.1866253292316654</v>
+        <v>0.1866253292316653</v>
       </c>
       <c r="AX17">
         <v>-0.06280809340857121</v>
       </c>
       <c r="AY17">
-        <v>0.4803080549240022</v>
+        <v>0.4803080549240021</v>
       </c>
       <c r="AZ17">
         <v>-0.1234717430003114</v>
@@ -4050,7 +4050,7 @@
         <v>0.2104828190565123</v>
       </c>
       <c r="BC17">
-        <v>0.3530856088729388</v>
+        <v>0.3530856088729387</v>
       </c>
       <c r="BD17">
         <v>0.3381951671872974</v>
@@ -4077,7 +4077,7 @@
         <v>-0.1188952324046603</v>
       </c>
       <c r="BL17">
-        <v>-0.1054665809368437</v>
+        <v>-0.1054665809368436</v>
       </c>
       <c r="BM17">
         <v>0.2157287675247491</v>
@@ -4089,13 +4089,13 @@
         <v>0.5433100100395944</v>
       </c>
       <c r="BP17">
-        <v>-0.08845447304384976</v>
+        <v>-0.08845447304384975</v>
       </c>
       <c r="BQ17">
         <v>0.1854269194139307</v>
       </c>
       <c r="BR17">
-        <v>-0.061577002155798</v>
+        <v>-0.06157700215579801</v>
       </c>
     </row>
     <row r="18">
@@ -4118,13 +4118,13 @@
         <v>0.6337775180682088</v>
       </c>
       <c r="G18">
-        <v>0.1780829562339614</v>
+        <v>0.1780829562339613</v>
       </c>
       <c r="H18">
         <v>0.2886977392842954</v>
       </c>
       <c r="I18">
-        <v>0.02816029602196699</v>
+        <v>0.02816029602196696</v>
       </c>
       <c r="J18">
         <v>0.367472663814325</v>
@@ -4333,7 +4333,7 @@
         <v>0.2254183312510533</v>
       </c>
       <c r="H19">
-        <v>0.1073348257594222</v>
+        <v>0.1073348257594221</v>
       </c>
       <c r="I19">
         <v>0.1432567549593635</v>
@@ -4542,13 +4542,13 @@
         <v>0.2893419269950067</v>
       </c>
       <c r="G20">
-        <v>0.2867880056649192</v>
+        <v>0.2867880056649191</v>
       </c>
       <c r="H20">
         <v>0.3190849431210687</v>
       </c>
       <c r="I20">
-        <v>0.1458067516771154</v>
+        <v>0.1458067516771153</v>
       </c>
       <c r="J20">
         <v>0.3325584194812907</v>
@@ -4754,13 +4754,13 @@
         <v>0.2955794119549575</v>
       </c>
       <c r="G21">
-        <v>0.05175875497351325</v>
+        <v>0.05175875497351324</v>
       </c>
       <c r="H21">
-        <v>0.07711563041555274</v>
+        <v>0.07711563041555272</v>
       </c>
       <c r="I21">
-        <v>0.07877497873776193</v>
+        <v>0.07877497873776194</v>
       </c>
       <c r="J21">
         <v>0.2764290725187684</v>
@@ -4954,7 +4954,7 @@
         <v>0.3093857877931815</v>
       </c>
       <c r="C22">
-        <v>0.2342868726029402</v>
+        <v>0.2342868726029401</v>
       </c>
       <c r="D22">
         <v>0.1997026763952917</v>
@@ -4966,7 +4966,7 @@
         <v>0.4494060080768073</v>
       </c>
       <c r="G22">
-        <v>-0.04065188940373561</v>
+        <v>-0.04065188940373562</v>
       </c>
       <c r="H22">
         <v>0.1587531572739671</v>
@@ -4975,7 +4975,7 @@
         <v>0.2481469840586732</v>
       </c>
       <c r="J22">
-        <v>0.1992659193635914</v>
+        <v>0.1992659193635913</v>
       </c>
       <c r="K22">
         <v>0.1680939821377576</v>
@@ -5163,7 +5163,7 @@
         <v>0.1280385491789417</v>
       </c>
       <c r="B23">
-        <v>0.3747926604339863</v>
+        <v>0.3747926604339864</v>
       </c>
       <c r="C23">
         <v>0.4019066637526973</v>
@@ -5199,7 +5199,7 @@
         <v>0.2200046130026323</v>
       </c>
       <c r="N23">
-        <v>0.09485941173305443</v>
+        <v>0.09485941173305441</v>
       </c>
       <c r="O23">
         <v>0.185110901762722</v>
@@ -5384,13 +5384,13 @@
         <v>0.1318978522397696</v>
       </c>
       <c r="E24">
-        <v>0.0001185471298084199</v>
+        <v>0.0001185471298084107</v>
       </c>
       <c r="F24">
         <v>0.2466980502634007</v>
       </c>
       <c r="G24">
-        <v>0.1629002712338486</v>
+        <v>0.1629002712338485</v>
       </c>
       <c r="H24">
         <v>0.2566711675832973</v>
@@ -5414,7 +5414,7 @@
         <v>0.1508920821087588</v>
       </c>
       <c r="O24">
-        <v>0.1498428071906256</v>
+        <v>0.1498428071906257</v>
       </c>
       <c r="P24">
         <v>0.07095864806961596</v>
@@ -5593,7 +5593,7 @@
         <v>0.384684626027505</v>
       </c>
       <c r="D25">
-        <v>0.3742409163349652</v>
+        <v>0.3742409163349653</v>
       </c>
       <c r="E25">
         <v>0.4270509137827634</v>
@@ -5602,7 +5602,7 @@
         <v>0.5144931870954053</v>
       </c>
       <c r="G25">
-        <v>0.0168276070000573</v>
+        <v>0.01682760700005729</v>
       </c>
       <c r="H25">
         <v>0.324192690805418</v>
@@ -5614,10 +5614,10 @@
         <v>0.2665666506512801</v>
       </c>
       <c r="K25">
-        <v>0.2519458645445983</v>
+        <v>0.2519458645445982</v>
       </c>
       <c r="L25">
-        <v>0.3968034444773813</v>
+        <v>0.3968034444773812</v>
       </c>
       <c r="M25">
         <v>0.292048468538363</v>
@@ -5814,7 +5814,7 @@
         <v>0.4534277500687597</v>
       </c>
       <c r="G26">
-        <v>0.04726366986913484</v>
+        <v>0.04726366986913481</v>
       </c>
       <c r="H26">
         <v>0.1904505033669596</v>
@@ -6023,7 +6023,7 @@
         <v>0.3908686300107879</v>
       </c>
       <c r="F27">
-        <v>0.09377794132571458</v>
+        <v>0.0937779413257146</v>
       </c>
       <c r="G27">
         <v>0.3722087524418143</v>
@@ -6032,7 +6032,7 @@
         <v>0.3922021363722752</v>
       </c>
       <c r="I27">
-        <v>0.1056684750221368</v>
+        <v>0.1056684750221367</v>
       </c>
       <c r="J27">
         <v>0.2093428326550113</v>
@@ -6041,7 +6041,7 @@
         <v>0.1780482017846694</v>
       </c>
       <c r="L27">
-        <v>-0.04322159410190252</v>
+        <v>-0.04322159410190254</v>
       </c>
       <c r="M27">
         <v>0.1596041801268009</v>
@@ -6050,7 +6050,7 @@
         <v>-0.1044124917736231</v>
       </c>
       <c r="O27">
-        <v>-0.06335395718497462</v>
+        <v>-0.06335395718497461</v>
       </c>
       <c r="P27">
         <v>0.1914991825567392</v>
@@ -6235,7 +6235,7 @@
         <v>0.3700644453170492</v>
       </c>
       <c r="F28">
-        <v>0.2856433804644709</v>
+        <v>0.285643380464471</v>
       </c>
       <c r="G28">
         <v>0.2259795705239566</v>
@@ -6256,13 +6256,13 @@
         <v>0.1584229328868029</v>
       </c>
       <c r="M28">
-        <v>0.1298318335949169</v>
+        <v>0.1298318335949168</v>
       </c>
       <c r="N28">
         <v>-0.01628903088772804</v>
       </c>
       <c r="O28">
-        <v>0.01970248164625295</v>
+        <v>0.01970248164625297</v>
       </c>
       <c r="P28">
         <v>0.2872945603727709</v>
@@ -6438,7 +6438,7 @@
         <v>0.2378405763098279</v>
       </c>
       <c r="C29">
-        <v>0.1890404768265991</v>
+        <v>0.189040476826599</v>
       </c>
       <c r="D29">
         <v>0.173066492373427</v>
@@ -6465,16 +6465,16 @@
         <v>0.1443920263172198</v>
       </c>
       <c r="L29">
-        <v>-0.001469485171316012</v>
+        <v>-0.001469485171316037</v>
       </c>
       <c r="M29">
-        <v>0.05247257347428654</v>
+        <v>0.05247257347428656</v>
       </c>
       <c r="N29">
-        <v>-0.0237594098647113</v>
+        <v>-0.02375940986471131</v>
       </c>
       <c r="O29">
-        <v>-0.04553184283102019</v>
+        <v>-0.04553184283102017</v>
       </c>
       <c r="P29">
         <v>0.1757643589103952</v>
@@ -6662,7 +6662,7 @@
         <v>0.1582527692127227</v>
       </c>
       <c r="G30">
-        <v>0.3981327316467003</v>
+        <v>0.3981327316467002</v>
       </c>
       <c r="H30">
         <v>0.3930601617098071</v>
@@ -6677,13 +6677,13 @@
         <v>0.2959299502763549</v>
       </c>
       <c r="L30">
-        <v>0.06638678206477679</v>
+        <v>0.06638678206477677</v>
       </c>
       <c r="M30">
         <v>0.2305744947426143</v>
       </c>
       <c r="N30">
-        <v>0.03502764141135334</v>
+        <v>0.03502764141135333</v>
       </c>
       <c r="O30">
         <v>0.03775911288614336</v>
@@ -6877,7 +6877,7 @@
         <v>0.1548837425855292</v>
       </c>
       <c r="H31">
-        <v>0.3945263109294574</v>
+        <v>0.3945263109294575</v>
       </c>
       <c r="I31">
         <v>0.1995233880796284</v>
@@ -6895,7 +6895,7 @@
         <v>0.3434941707036531</v>
       </c>
       <c r="N31">
-        <v>0.05752910517912828</v>
+        <v>0.05752910517912827</v>
       </c>
       <c r="O31">
         <v>0.1944235601943125</v>
@@ -7074,7 +7074,7 @@
         <v>0.5022736085894423</v>
       </c>
       <c r="C32">
-        <v>0.340779336680734</v>
+        <v>0.3407793366807339</v>
       </c>
       <c r="D32">
         <v>0.1593786962650585</v>
@@ -7092,7 +7092,7 @@
         <v>0.3288142634917523</v>
       </c>
       <c r="I32">
-        <v>0.07874373883352849</v>
+        <v>0.07874373883352848</v>
       </c>
       <c r="J32">
         <v>0.2915370876921702</v>
@@ -7101,7 +7101,7 @@
         <v>0.377213070632275</v>
       </c>
       <c r="L32">
-        <v>0.3875480515633799</v>
+        <v>0.3875480515633798</v>
       </c>
       <c r="M32">
         <v>0.468514165744501</v>
@@ -7319,7 +7319,7 @@
         <v>0.2747932190617494</v>
       </c>
       <c r="N33">
-        <v>-0.02988232081870757</v>
+        <v>-0.02988232081870758</v>
       </c>
       <c r="O33">
         <v>0.155622368147797</v>
@@ -7513,13 +7513,13 @@
         <v>0.1680240932769843</v>
       </c>
       <c r="H34">
-        <v>0.4185676757337321</v>
+        <v>0.418567675733732</v>
       </c>
       <c r="I34">
         <v>0.2679589475444918</v>
       </c>
       <c r="J34">
-        <v>0.4704768313232849</v>
+        <v>0.4704768313232848</v>
       </c>
       <c r="K34">
         <v>0.3055066322579303</v>
@@ -7922,7 +7922,7 @@
         <v>0.3199806262488953</v>
       </c>
       <c r="C36">
-        <v>0.5533588522479808</v>
+        <v>0.5533588522479806</v>
       </c>
       <c r="D36">
         <v>0.4053702324558843</v>
@@ -7937,7 +7937,7 @@
         <v>0.669206595485008</v>
       </c>
       <c r="H36">
-        <v>0.7824173238569316</v>
+        <v>0.7824173238569315</v>
       </c>
       <c r="I36">
         <v>0.718527998614238</v>
@@ -8358,7 +8358,7 @@
         <v>0.5754051022063299</v>
       </c>
       <c r="G38">
-        <v>0.07594167062982217</v>
+        <v>0.07594167062982214</v>
       </c>
       <c r="H38">
         <v>0.3473267116254769</v>
@@ -8594,7 +8594,7 @@
         <v>-0.01742302320070251</v>
       </c>
       <c r="O39">
-        <v>0.02631463070978511</v>
+        <v>0.02631463070978512</v>
       </c>
       <c r="P39">
         <v>0.3286231914362282</v>
@@ -8770,10 +8770,10 @@
         <v>0.4448455725658337</v>
       </c>
       <c r="C40">
-        <v>0.7425838147914058</v>
+        <v>0.7425838147914059</v>
       </c>
       <c r="D40">
-        <v>0.4319982175357553</v>
+        <v>0.4319982175357552</v>
       </c>
       <c r="E40">
         <v>0.3052890151364571</v>
@@ -8782,7 +8782,7 @@
         <v>0.3344695643263639</v>
       </c>
       <c r="G40">
-        <v>0.05007678765066133</v>
+        <v>0.05007678765066136</v>
       </c>
       <c r="H40">
         <v>0.3967429671686492</v>
@@ -8794,7 +8794,7 @@
         <v>0.3239071411455954</v>
       </c>
       <c r="K40">
-        <v>0.1864148687122232</v>
+        <v>0.1864148687122231</v>
       </c>
       <c r="L40">
         <v>0.1867385453430367</v>
@@ -8806,10 +8806,10 @@
         <v>0.01662999162140247</v>
       </c>
       <c r="O40">
-        <v>0.09563100436652007</v>
+        <v>0.09563100436652008</v>
       </c>
       <c r="P40">
-        <v>0.06375690611788008</v>
+        <v>0.0637569061178801</v>
       </c>
       <c r="Q40">
         <v>0.1857669104707274</v>
@@ -8988,7 +8988,7 @@
         <v>0.274936316129236</v>
       </c>
       <c r="E41">
-        <v>-0.1408601764411822</v>
+        <v>-0.1408601764411823</v>
       </c>
       <c r="F41">
         <v>0.1454928952403934</v>
@@ -9003,7 +9003,7 @@
         <v>0.3571687901301924</v>
       </c>
       <c r="J41">
-        <v>0.2141468706699332</v>
+        <v>0.2141468706699333</v>
       </c>
       <c r="K41">
         <v>0.2756260663158595</v>
@@ -9012,13 +9012,13 @@
         <v>0.1385554772321807</v>
       </c>
       <c r="M41">
-        <v>0.1951875826103697</v>
+        <v>0.1951875826103696</v>
       </c>
       <c r="N41">
         <v>0.02188064540660897</v>
       </c>
       <c r="O41">
-        <v>0.07966906951694713</v>
+        <v>0.07966906951694715</v>
       </c>
       <c r="P41">
         <v>0.1629625193673907</v>
@@ -9191,25 +9191,25 @@
         <v>0.06668308712583206</v>
       </c>
       <c r="B42">
-        <v>0.04140704974098997</v>
+        <v>0.04140704974098999</v>
       </c>
       <c r="C42">
         <v>-0.01318299461690276</v>
       </c>
       <c r="D42">
-        <v>-0.03700588076986108</v>
+        <v>-0.03700588076986109</v>
       </c>
       <c r="E42">
-        <v>-0.06294638134902261</v>
+        <v>-0.06294638134902258</v>
       </c>
       <c r="F42">
         <v>0.2824273394623477</v>
       </c>
       <c r="G42">
-        <v>-0.02657441326273877</v>
+        <v>-0.02657441326273876</v>
       </c>
       <c r="H42">
-        <v>-0.07356233600256593</v>
+        <v>-0.07356233600256591</v>
       </c>
       <c r="I42">
         <v>-0.109063262123377</v>
@@ -9218,7 +9218,7 @@
         <v>0.06715600735259596</v>
       </c>
       <c r="K42">
-        <v>0.1128052291875371</v>
+        <v>0.112805229187537</v>
       </c>
       <c r="L42">
         <v>0.4108753219822919</v>
@@ -9233,7 +9233,7 @@
         <v>0.516363842997219</v>
       </c>
       <c r="P42">
-        <v>0.4158137120622744</v>
+        <v>0.4158137120622743</v>
       </c>
       <c r="Q42">
         <v>0.2401757416090075</v>
@@ -9403,7 +9403,7 @@
         <v>-0.1147847982747518</v>
       </c>
       <c r="B43">
-        <v>-0.2073042002127984</v>
+        <v>-0.2073042002127985</v>
       </c>
       <c r="C43">
         <v>-0.1114386403000996</v>
@@ -9412,7 +9412,7 @@
         <v>-0.104444670628245</v>
       </c>
       <c r="E43">
-        <v>-0.08617993521812582</v>
+        <v>-0.08617993521812584</v>
       </c>
       <c r="F43">
         <v>-0.3176735834889085</v>
@@ -9421,22 +9421,22 @@
         <v>0.1731964102869479</v>
       </c>
       <c r="H43">
-        <v>-0.006998604390283237</v>
+        <v>-0.006998604390283248</v>
       </c>
       <c r="I43">
         <v>-0.1865325626653916</v>
       </c>
       <c r="J43">
-        <v>-0.07912030969390711</v>
+        <v>-0.07912030969390708</v>
       </c>
       <c r="K43">
-        <v>-0.05768547851937358</v>
+        <v>-0.05768547851937354</v>
       </c>
       <c r="L43">
         <v>-0.2615369961821907</v>
       </c>
       <c r="M43">
-        <v>-0.02793787257067175</v>
+        <v>-0.02793787257067176</v>
       </c>
       <c r="N43">
         <v>-0.1334038173958635</v>
@@ -9445,7 +9445,7 @@
         <v>-0.1025829084890252</v>
       </c>
       <c r="P43">
-        <v>0.03675417648683978</v>
+        <v>0.03675417648683979</v>
       </c>
       <c r="Q43">
         <v>-0.0716346764081144</v>
@@ -9615,19 +9615,19 @@
         <v>0.01777030934931751</v>
       </c>
       <c r="B44">
-        <v>0.08300260959817199</v>
+        <v>0.083002609598172</v>
       </c>
       <c r="C44">
-        <v>-0.001635977054502158</v>
+        <v>-0.001635977054502163</v>
       </c>
       <c r="D44">
         <v>0.09864629643210286</v>
       </c>
       <c r="E44">
-        <v>0.06918864330727771</v>
+        <v>0.06918864330727774</v>
       </c>
       <c r="F44">
-        <v>-0.02945399502968301</v>
+        <v>-0.029453995029683</v>
       </c>
       <c r="G44">
         <v>0.1712458286357201</v>
@@ -9636,19 +9636,19 @@
         <v>0.1353233426967667</v>
       </c>
       <c r="I44">
-        <v>0.07990970319665273</v>
+        <v>0.07990970319665272</v>
       </c>
       <c r="J44">
-        <v>0.06302232280880848</v>
+        <v>0.06302232280880846</v>
       </c>
       <c r="K44">
         <v>0.2000226096475824</v>
       </c>
       <c r="L44">
-        <v>-0.07110016303754101</v>
+        <v>-0.07110016303754103</v>
       </c>
       <c r="M44">
-        <v>0.01415313972759976</v>
+        <v>0.01415313972759977</v>
       </c>
       <c r="N44">
         <v>-0.04432232851642876</v>
@@ -9830,7 +9830,7 @@
         <v>0.7580741145508794</v>
       </c>
       <c r="C45">
-        <v>0.4058312002974861</v>
+        <v>0.405831200297486</v>
       </c>
       <c r="D45">
         <v>0.3108419388701779</v>
@@ -9839,16 +9839,16 @@
         <v>0.6471336984139858</v>
       </c>
       <c r="F45">
-        <v>0.2794598291751212</v>
+        <v>0.2794598291751213</v>
       </c>
       <c r="G45">
-        <v>0.03332074660277219</v>
+        <v>0.0333207466027722</v>
       </c>
       <c r="H45">
         <v>0.320674638245305</v>
       </c>
       <c r="I45">
-        <v>0.06218014448839663</v>
+        <v>0.0621801444883966</v>
       </c>
       <c r="J45">
         <v>0.2384225514466057</v>
@@ -9863,7 +9863,7 @@
         <v>0.2875543737046246</v>
       </c>
       <c r="N45">
-        <v>0.0565510457981351</v>
+        <v>0.05655104579813511</v>
       </c>
       <c r="O45">
         <v>0.1444694234228835</v>
@@ -10045,7 +10045,7 @@
         <v>0.1007691536068129</v>
       </c>
       <c r="D46">
-        <v>0.082055304171447</v>
+        <v>0.08205530417144699</v>
       </c>
       <c r="E46">
         <v>-0.3044897432731903</v>
@@ -10263,16 +10263,16 @@
         <v>0.1148272279333186</v>
       </c>
       <c r="F47">
-        <v>0.6990709181809003</v>
+        <v>0.6990709181809004</v>
       </c>
       <c r="G47">
-        <v>-0.02395491118527681</v>
+        <v>-0.02395491118527684</v>
       </c>
       <c r="H47">
         <v>0.1489585813640912</v>
       </c>
       <c r="I47">
-        <v>0.08148932196101265</v>
+        <v>0.08148932196101262</v>
       </c>
       <c r="J47">
         <v>0.3245474756317687</v>
@@ -10478,7 +10478,7 @@
         <v>-0.5516781103030769</v>
       </c>
       <c r="G48">
-        <v>0.09675982119206325</v>
+        <v>0.09675982119206326</v>
       </c>
       <c r="H48">
         <v>-0.2421385332059808</v>
@@ -10496,7 +10496,7 @@
         <v>-0.4200805923429345</v>
       </c>
       <c r="M48">
-        <v>-0.2652900877362808</v>
+        <v>-0.2652900877362809</v>
       </c>
       <c r="N48">
         <v>-0.1249496951854896</v>
@@ -10687,16 +10687,16 @@
         <v>0.2831542231493676</v>
       </c>
       <c r="F49">
-        <v>-0.0373538028290351</v>
+        <v>-0.03735380282903509</v>
       </c>
       <c r="G49">
         <v>0.3272342425022901</v>
       </c>
       <c r="H49">
-        <v>0.2343859166090143</v>
+        <v>0.2343859166090144</v>
       </c>
       <c r="I49">
-        <v>0.04354670782699682</v>
+        <v>0.04354670782699681</v>
       </c>
       <c r="J49">
         <v>0.114881793402044</v>
@@ -10905,7 +10905,7 @@
         <v>0.1642806345476137</v>
       </c>
       <c r="H50">
-        <v>0.4093770498169907</v>
+        <v>0.4093770498169906</v>
       </c>
       <c r="I50">
         <v>0.2539707476851705</v>
@@ -10929,7 +10929,7 @@
         <v>0.2377512557560051</v>
       </c>
       <c r="P50">
-        <v>0.1866253292316654</v>
+        <v>0.1866253292316653</v>
       </c>
       <c r="Q50">
         <v>0.379552961446906</v>
@@ -11099,7 +11099,7 @@
         <v>0.04615430149171809</v>
       </c>
       <c r="B51">
-        <v>-0.04254991443654318</v>
+        <v>-0.04254991443654316</v>
       </c>
       <c r="C51">
         <v>0.2080983847838686</v>
@@ -11132,7 +11132,7 @@
         <v>0.2030015746446936</v>
       </c>
       <c r="M51">
-        <v>0.1747250605082012</v>
+        <v>0.1747250605082011</v>
       </c>
       <c r="N51">
         <v>0.06327874369937106</v>
@@ -11314,31 +11314,31 @@
         <v>0.1115269693982819</v>
       </c>
       <c r="C52">
-        <v>0.03447326115644708</v>
+        <v>0.03447326115644706</v>
       </c>
       <c r="D52">
         <v>0.08929657813578637</v>
       </c>
       <c r="E52">
-        <v>-0.05361650610630309</v>
+        <v>-0.05361650610630308</v>
       </c>
       <c r="F52">
         <v>0.4084975675579184</v>
       </c>
       <c r="G52">
-        <v>0.08924119149508909</v>
+        <v>0.08924119149508908</v>
       </c>
       <c r="H52">
         <v>0.08089689614478054</v>
       </c>
       <c r="I52">
-        <v>0.03588544089295026</v>
+        <v>0.03588544089295023</v>
       </c>
       <c r="J52">
         <v>0.1978298550344983</v>
       </c>
       <c r="K52">
-        <v>0.3261366270908865</v>
+        <v>0.3261366270908864</v>
       </c>
       <c r="L52">
         <v>0.512876694653847</v>
@@ -11353,7 +11353,7 @@
         <v>0.519245134868895</v>
       </c>
       <c r="P52">
-        <v>0.4803080549240022</v>
+        <v>0.4803080549240021</v>
       </c>
       <c r="Q52">
         <v>0.4031904734998532</v>
@@ -11529,16 +11529,16 @@
         <v>-0.1218801066767945</v>
       </c>
       <c r="D53">
-        <v>-0.1646666226593624</v>
+        <v>-0.1646666226593623</v>
       </c>
       <c r="E53">
-        <v>-0.03106671980222752</v>
+        <v>-0.03106671980222751</v>
       </c>
       <c r="F53">
         <v>-0.3754237934945821</v>
       </c>
       <c r="G53">
-        <v>-0.01224287983443979</v>
+        <v>-0.01224287983443975</v>
       </c>
       <c r="H53">
         <v>-0.126405777643757</v>
@@ -11550,16 +11550,16 @@
         <v>-0.2090881636179694</v>
       </c>
       <c r="K53">
-        <v>-0.2299103931914541</v>
+        <v>-0.229910393191454</v>
       </c>
       <c r="L53">
         <v>-0.3608050487313455</v>
       </c>
       <c r="M53">
-        <v>-0.2481372684173339</v>
+        <v>-0.248137268417334</v>
       </c>
       <c r="N53">
-        <v>-0.2098012047863404</v>
+        <v>-0.2098012047863405</v>
       </c>
       <c r="O53">
         <v>-0.2354593042501343</v>
@@ -11759,13 +11759,13 @@
         <v>0.1461113020004297</v>
       </c>
       <c r="J54">
-        <v>0.2381776426920908</v>
+        <v>0.2381776426920907</v>
       </c>
       <c r="K54">
         <v>0.2161715738415062</v>
       </c>
       <c r="L54">
-        <v>0.09293590569513338</v>
+        <v>0.09293590569513335</v>
       </c>
       <c r="M54">
         <v>0.1076745656347624</v>
@@ -11774,7 +11774,7 @@
         <v>-0.07331576687296533</v>
       </c>
       <c r="O54">
-        <v>-0.02363372459415723</v>
+        <v>-0.0236337245941572</v>
       </c>
       <c r="P54">
         <v>0.2006964802142066</v>
@@ -11983,7 +11983,7 @@
         <v>0.2571776780732139</v>
       </c>
       <c r="N55">
-        <v>0.05185979565942452</v>
+        <v>0.05185979565942453</v>
       </c>
       <c r="O55">
         <v>0.1768154293616226</v>
@@ -12180,10 +12180,10 @@
         <v>0.268571628492587</v>
       </c>
       <c r="I56">
-        <v>0.1133503853564954</v>
+        <v>0.1133503853564953</v>
       </c>
       <c r="J56">
-        <v>0.2817079303319186</v>
+        <v>0.2817079303319185</v>
       </c>
       <c r="K56">
         <v>0.3648342546299327</v>
@@ -12201,7 +12201,7 @@
         <v>0.439413135161783</v>
       </c>
       <c r="P56">
-        <v>0.3530856088729388</v>
+        <v>0.3530856088729387</v>
       </c>
       <c r="Q56">
         <v>0.7435437870116052</v>
@@ -12583,13 +12583,13 @@
         <v>0.1363254050439551</v>
       </c>
       <c r="B58">
-        <v>0.1628392400525995</v>
+        <v>0.1628392400525996</v>
       </c>
       <c r="C58">
-        <v>0.0386737019287409</v>
+        <v>0.03867370192874089</v>
       </c>
       <c r="D58">
-        <v>0.07726081843365447</v>
+        <v>0.07726081843365448</v>
       </c>
       <c r="E58">
         <v>0.1011372004728547</v>
@@ -12598,13 +12598,13 @@
         <v>0.232171782664603</v>
       </c>
       <c r="G58">
-        <v>0.2839764569752609</v>
+        <v>0.2839764569752608</v>
       </c>
       <c r="H58">
-        <v>0.1812716594129277</v>
+        <v>0.1812716594129276</v>
       </c>
       <c r="I58">
-        <v>0.02414658646128147</v>
+        <v>0.02414658646128145</v>
       </c>
       <c r="J58">
         <v>0.2640509744314741</v>
@@ -12810,19 +12810,19 @@
         <v>0.6814853253303261</v>
       </c>
       <c r="G59">
-        <v>0.1063799217300708</v>
+        <v>0.1063799217300707</v>
       </c>
       <c r="H59">
         <v>0.2567805245780702</v>
       </c>
       <c r="I59">
-        <v>0.03873160958281665</v>
+        <v>0.03873160958281661</v>
       </c>
       <c r="J59">
         <v>0.3015498320911594</v>
       </c>
       <c r="K59">
-        <v>0.384582580708385</v>
+        <v>0.3845825807083849</v>
       </c>
       <c r="L59">
         <v>0.6551504599482877</v>
@@ -13025,7 +13025,7 @@
         <v>0.1780424289057974</v>
       </c>
       <c r="H60">
-        <v>0.418144557408371</v>
+        <v>0.4181445574083709</v>
       </c>
       <c r="I60">
         <v>0.1572785142159224</v>
@@ -13231,7 +13231,7 @@
         <v>0.2602454537886317</v>
       </c>
       <c r="F61">
-        <v>0.491712763457485</v>
+        <v>0.4917127634574851</v>
       </c>
       <c r="G61">
         <v>0.1575919130509088</v>
@@ -13249,7 +13249,7 @@
         <v>0.3371603254621376</v>
       </c>
       <c r="L61">
-        <v>0.4946887115785982</v>
+        <v>0.4946887115785983</v>
       </c>
       <c r="M61">
         <v>0.4075905980047503</v>
@@ -13431,25 +13431,25 @@
         <v>-0.1711291938474344</v>
       </c>
       <c r="B62">
-        <v>-0.06138882052757016</v>
+        <v>-0.06138882052757017</v>
       </c>
       <c r="C62">
-        <v>-0.03533065083601121</v>
+        <v>-0.0353306508360112</v>
       </c>
       <c r="D62">
         <v>-0.001143553574107182</v>
       </c>
       <c r="E62">
-        <v>0.005968783171217401</v>
+        <v>0.005968783171217395</v>
       </c>
       <c r="F62">
         <v>-0.1651947968585291</v>
       </c>
       <c r="G62">
-        <v>0.01923911953388723</v>
+        <v>0.01923911953388722</v>
       </c>
       <c r="H62">
-        <v>-0.02380478319921953</v>
+        <v>-0.02380478319921954</v>
       </c>
       <c r="I62">
         <v>-0.03409080149320637</v>
@@ -13458,19 +13458,19 @@
         <v>-0.1691755879259148</v>
       </c>
       <c r="K62">
-        <v>-0.02996769418967704</v>
+        <v>-0.02996769418967705</v>
       </c>
       <c r="L62">
         <v>-0.1432419614880656</v>
       </c>
       <c r="M62">
-        <v>0.00323084973881806</v>
+        <v>0.003230849738818055</v>
       </c>
       <c r="N62">
-        <v>0.007790922999669946</v>
+        <v>0.007790922999669953</v>
       </c>
       <c r="O62">
-        <v>-0.08283697910961772</v>
+        <v>-0.08283697910961774</v>
       </c>
       <c r="P62">
         <v>-0.0541166511664647</v>
@@ -13658,7 +13658,7 @@
         <v>0.1674301611853785</v>
       </c>
       <c r="G63">
-        <v>0.3307968423322505</v>
+        <v>0.3307968423322504</v>
       </c>
       <c r="H63">
         <v>0.3205191477931733</v>
@@ -13673,7 +13673,7 @@
         <v>0.2386873527495568</v>
       </c>
       <c r="L63">
-        <v>0.06113020842194036</v>
+        <v>0.06113020842194034</v>
       </c>
       <c r="M63">
         <v>0.1935939764012155</v>
@@ -13682,7 +13682,7 @@
         <v>-0.05896414389556855</v>
       </c>
       <c r="O63">
-        <v>-0.03692313850820914</v>
+        <v>-0.03692313850820912</v>
       </c>
       <c r="P63">
         <v>0.2256249649194618</v>
@@ -13855,7 +13855,7 @@
         <v>-0.1831440162542547</v>
       </c>
       <c r="B64">
-        <v>-0.1571188328370876</v>
+        <v>-0.1571188328370877</v>
       </c>
       <c r="C64">
         <v>-0.155519279784181</v>
@@ -14067,13 +14067,13 @@
         <v>-0.1550872998157699</v>
       </c>
       <c r="B65">
-        <v>0.05000191297444864</v>
+        <v>0.05000191297444862</v>
       </c>
       <c r="C65">
-        <v>0.004640505707432534</v>
+        <v>0.004640505707432542</v>
       </c>
       <c r="D65">
-        <v>0.00975439863784475</v>
+        <v>0.009754398637844759</v>
       </c>
       <c r="E65">
         <v>0.1071558186950637</v>
@@ -14082,13 +14082,13 @@
         <v>-0.2439814081748835</v>
       </c>
       <c r="G65">
-        <v>0.1262985819990905</v>
+        <v>0.1262985819990906</v>
       </c>
       <c r="H65">
-        <v>0.09039673152432014</v>
+        <v>0.09039673152432016</v>
       </c>
       <c r="I65">
-        <v>-0.06110322876470808</v>
+        <v>-0.06110322876470806</v>
       </c>
       <c r="J65">
         <v>-0.1271858764467076</v>
@@ -14109,7 +14109,7 @@
         <v>-0.281260163617128</v>
       </c>
       <c r="P65">
-        <v>-0.1054665809368437</v>
+        <v>-0.1054665809368436</v>
       </c>
       <c r="Q65">
         <v>-0.0819927962386572</v>
@@ -14288,7 +14288,7 @@
         <v>0.4577821850040105</v>
       </c>
       <c r="E66">
-        <v>0.4928148042656748</v>
+        <v>0.4928148042656749</v>
       </c>
       <c r="F66">
         <v>0.549129519308499</v>
@@ -14300,7 +14300,7 @@
         <v>0.4861899489125276</v>
       </c>
       <c r="I66">
-        <v>0.2322623071465211</v>
+        <v>0.232262307146521</v>
       </c>
       <c r="J66">
         <v>0.3825981894399664</v>
@@ -14315,7 +14315,7 @@
         <v>0.3062480564408996</v>
       </c>
       <c r="N66">
-        <v>0.07272273261731013</v>
+        <v>0.07272273261731015</v>
       </c>
       <c r="O66">
         <v>0.196927722700939</v>
@@ -14491,7 +14491,7 @@
         <v>0.03778193024998786</v>
       </c>
       <c r="B67">
-        <v>-0.08262493891472335</v>
+        <v>-0.08262493891472332</v>
       </c>
       <c r="C67">
         <v>0.2141866448501853</v>
@@ -14524,7 +14524,7 @@
         <v>0.2393550318062219</v>
       </c>
       <c r="M67">
-        <v>0.272987054290026</v>
+        <v>0.2729870542900259</v>
       </c>
       <c r="N67">
         <v>0.1073152491493141</v>
@@ -14712,19 +14712,19 @@
         <v>0.1002882953308038</v>
       </c>
       <c r="E68">
-        <v>-0.002881243690523026</v>
+        <v>-0.002881243690523003</v>
       </c>
       <c r="F68">
         <v>0.5390367212616027</v>
       </c>
       <c r="G68">
-        <v>0.008432696919855969</v>
+        <v>0.008432696919855954</v>
       </c>
       <c r="H68">
-        <v>0.05067950120329013</v>
+        <v>0.05067950120329014</v>
       </c>
       <c r="I68">
-        <v>-0.007052858075198342</v>
+        <v>-0.007052858075198376</v>
       </c>
       <c r="J68">
         <v>0.2233007749718864</v>
@@ -14736,7 +14736,7 @@
         <v>0.6684191897525185</v>
       </c>
       <c r="M68">
-        <v>0.5589902434566772</v>
+        <v>0.5589902434566774</v>
       </c>
       <c r="N68">
         <v>0.7042681003898076</v>
@@ -14930,7 +14930,7 @@
         <v>-0.4796485521289377</v>
       </c>
       <c r="G69">
-        <v>0.09491221966426862</v>
+        <v>0.09491221966426865</v>
       </c>
       <c r="H69">
         <v>-0.1489923025737508</v>
@@ -14942,13 +14942,13 @@
         <v>-0.199667786962586</v>
       </c>
       <c r="K69">
-        <v>-0.1868564435155315</v>
+        <v>-0.1868564435155314</v>
       </c>
       <c r="L69">
         <v>-0.4014058711894786</v>
       </c>
       <c r="M69">
-        <v>-0.2131897885463789</v>
+        <v>-0.213189788546379</v>
       </c>
       <c r="N69">
         <v>-0.1789698023885791</v>
@@ -14957,7 +14957,7 @@
         <v>-0.2165179904061903</v>
       </c>
       <c r="P69">
-        <v>-0.08845447304384976</v>
+        <v>-0.08845447304384975</v>
       </c>
       <c r="Q69">
         <v>-0.233440770113508</v>
@@ -15139,34 +15139,34 @@
         <v>0.238399746788859</v>
       </c>
       <c r="F70">
-        <v>0.06875546642267573</v>
+        <v>0.06875546642267574</v>
       </c>
       <c r="G70">
         <v>0.244995882875642</v>
       </c>
       <c r="H70">
-        <v>0.2925884938953603</v>
+        <v>0.2925884938953604</v>
       </c>
       <c r="I70">
         <v>0.1109872817975772</v>
       </c>
       <c r="J70">
-        <v>0.1632746283646629</v>
+        <v>0.1632746283646628</v>
       </c>
       <c r="K70">
         <v>0.2305187818356912</v>
       </c>
       <c r="L70">
-        <v>-0.03405685371166332</v>
+        <v>-0.03405685371166334</v>
       </c>
       <c r="M70">
-        <v>0.0741011234371247</v>
+        <v>0.07410112343712472</v>
       </c>
       <c r="N70">
-        <v>-0.09147567502842688</v>
+        <v>-0.09147567502842689</v>
       </c>
       <c r="O70">
-        <v>-0.1137884659488672</v>
+        <v>-0.1137884659488671</v>
       </c>
       <c r="P70">
         <v>0.1854269194139307</v>
@@ -15342,37 +15342,37 @@
         <v>0.1917090157141538</v>
       </c>
       <c r="C71">
-        <v>0.007397472887378596</v>
+        <v>0.007397472887378591</v>
       </c>
       <c r="D71">
-        <v>0.003736241288074699</v>
+        <v>0.00373624128807471</v>
       </c>
       <c r="E71">
         <v>0.1303050210974445</v>
       </c>
       <c r="F71">
-        <v>0.1926508084556657</v>
+        <v>0.1926508084556656</v>
       </c>
       <c r="G71">
         <v>-0.2318861461852715</v>
       </c>
       <c r="H71">
-        <v>0.02349517145619149</v>
+        <v>0.02349517145619151</v>
       </c>
       <c r="I71">
-        <v>-0.004119863853618199</v>
+        <v>-0.004119863853618197</v>
       </c>
       <c r="J71">
-        <v>0.02411196686783855</v>
+        <v>0.02411196686783851</v>
       </c>
       <c r="K71">
-        <v>-0.06186906461447747</v>
+        <v>-0.06186906461447744</v>
       </c>
       <c r="L71">
         <v>0.08558497084893145</v>
       </c>
       <c r="M71">
-        <v>-0.0428193697066622</v>
+        <v>-0.04281936970666218</v>
       </c>
       <c r="N71">
         <v>0.03967907082894034</v>
@@ -15381,7 +15381,7 @@
         <v>0.0300687360012118</v>
       </c>
       <c r="P71">
-        <v>-0.061577002155798</v>
+        <v>-0.06157700215579801</v>
       </c>
       <c r="Q71">
         <v>0.01495951174146273</v>
